--- a/xlsx/Power/p22.xlsx
+++ b/xlsx/Power/p22.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC23CA36-C1F7-4DA7-94E3-D72400D97F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46792B77-E4AF-4768-9880-6044B1BA7FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3B7641DA-A5C0-4754-89A8-0673DC78D0D2}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3B7641DA-A5C0-4754-89A8-0673DC78D0D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.18099999999999999</v>
       </c>
       <c r="C1">
-        <v>0.26</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D1">
-        <v>0.34200000000000003</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="E1">
-        <v>0.39600000000000002</v>
+        <v>0.188</v>
       </c>
       <c r="F1">
-        <v>0.43</v>
+        <v>0.252</v>
       </c>
       <c r="G1">
-        <v>0.52</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="H1">
-        <v>0.53600000000000003</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="I1">
-        <v>0.59</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="J1">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="C2">
-        <v>0.29699999999999999</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="D2">
-        <v>0.38100000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="E2">
-        <v>0.42599999999999999</v>
+        <v>0.218</v>
       </c>
       <c r="F2">
-        <v>0.45500000000000002</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="G2">
-        <v>0.54400000000000004</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="H2">
-        <v>0.57399999999999995</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="I2">
-        <v>0.626</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="J2">
-        <v>0.66800000000000004</v>
+        <v>0.54800000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="C3">
-        <v>0.20499999999999999</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="D3">
-        <v>0.25700000000000001</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="E3">
-        <v>0.314</v>
+        <v>0.318</v>
       </c>
       <c r="F3">
-        <v>0.32800000000000001</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="G3">
         <v>0.39500000000000002</v>
       </c>
       <c r="H3">
-        <v>0.40899999999999997</v>
+        <v>0.41</v>
       </c>
       <c r="I3">
         <v>0.46800000000000003</v>
       </c>
       <c r="J3">
-        <v>0.48799999999999999</v>
+        <v>0.49399999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.112</v>
+        <v>0.127</v>
       </c>
       <c r="B4">
-        <v>0.128</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="C4">
-        <v>0.17299999999999999</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="D4">
-        <v>0.20300000000000001</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="E4">
-        <v>0.27</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="F4">
-        <v>0.28799999999999998</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="G4">
-        <v>0.33900000000000002</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="H4">
-        <v>0.35599999999999998</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="I4">
         <v>0.41</v>
       </c>
       <c r="J4">
-        <v>0.41</v>
+        <v>0.41099999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="C5">
-        <v>7.1999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>6.8000000000000005E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>9.6000000000000002E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="F5">
-        <v>7.9000000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G5">
-        <v>0.105</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="H5">
-        <v>9.9000000000000005E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I5">
-        <v>0.106</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="J5">
-        <v>0.122</v>
+        <v>5.3999999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.216</v>
       </c>
       <c r="C6">
-        <v>0.32600000000000001</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="D6">
-        <v>0.40300000000000002</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="E6">
-        <v>0.44900000000000001</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="F6">
-        <v>0.48799999999999999</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="G6">
-        <v>0.58099999999999996</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="H6">
-        <v>0.61899999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="I6">
-        <v>0.66600000000000004</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="J6">
-        <v>0.69499999999999995</v>
+        <v>0.70799999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="C7">
-        <v>0.30599999999999999</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="D7">
-        <v>0.38400000000000001</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="E7">
-        <v>0.42399999999999999</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="F7">
-        <v>0.45700000000000002</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="G7">
-        <v>0.54500000000000004</v>
+        <v>0.53900000000000003</v>
       </c>
       <c r="H7">
         <v>0.58499999999999996</v>
       </c>
       <c r="I7">
-        <v>0.629</v>
+        <v>0.625</v>
       </c>
       <c r="J7">
-        <v>0.66800000000000004</v>
+        <v>0.66400000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="C8">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.151</v>
+        <v>1.2E-2</v>
       </c>
       <c r="E8">
-        <v>0.16600000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F8">
-        <v>0.157</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G8">
-        <v>0.21</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="H8">
-        <v>0.23899999999999999</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="I8">
-        <v>0.28000000000000003</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="J8">
-        <v>0.29699999999999999</v>
+        <v>3.7999999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="C9">
-        <v>0.127</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="D9">
-        <v>9.8000000000000004E-2</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="E9">
-        <v>0.09</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="F9">
-        <v>7.6999999999999999E-2</v>
+        <v>0.17</v>
       </c>
       <c r="G9">
-        <v>0.09</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="H9">
-        <v>0.106</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="I9">
-        <v>0.114</v>
+        <v>0.13</v>
       </c>
       <c r="J9">
-        <v>0.11899999999999999</v>
+        <v>0.129</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p22.xlsx
+++ b/xlsx/Power/p22.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46792B77-E4AF-4768-9880-6044B1BA7FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9DD3D8-9670-4A05-92E2-6A8C610F2A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3B7641DA-A5C0-4754-89A8-0673DC78D0D2}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3B7641DA-A5C0-4754-89A8-0673DC78D0D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,34 +398,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="B1">
         <v>0.18099999999999999</v>
       </c>
       <c r="C1">
-        <v>2.4E-2</v>
+        <v>0.26</v>
       </c>
       <c r="D1">
-        <v>8.8999999999999996E-2</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="E1">
-        <v>0.188</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="F1">
-        <v>0.252</v>
+        <v>0.43</v>
       </c>
       <c r="G1">
-        <v>0.35499999999999998</v>
+        <v>0.52</v>
       </c>
       <c r="H1">
-        <v>0.38700000000000001</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="I1">
-        <v>0.47699999999999998</v>
+        <v>0.59</v>
       </c>
       <c r="J1">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="C2">
-        <v>3.3000000000000002E-2</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="D2">
-        <v>0.105</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="E2">
-        <v>0.218</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="F2">
-        <v>0.28699999999999998</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="G2">
-        <v>0.39500000000000002</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="H2">
-        <v>0.41699999999999998</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="I2">
-        <v>0.52500000000000002</v>
+        <v>0.626</v>
       </c>
       <c r="J2">
-        <v>0.54800000000000004</v>
+        <v>0.66800000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="C3">
-        <v>0.23100000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="D3">
-        <v>0.26400000000000001</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="E3">
-        <v>0.318</v>
+        <v>0.314</v>
       </c>
       <c r="F3">
-        <v>0.33500000000000002</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="G3">
         <v>0.39500000000000002</v>
       </c>
       <c r="H3">
-        <v>0.41</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="I3">
         <v>0.46800000000000003</v>
       </c>
       <c r="J3">
-        <v>0.49399999999999999</v>
+        <v>0.48799999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.127</v>
+        <v>0.112</v>
       </c>
       <c r="B4">
-        <v>0.13700000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="C4">
-        <v>0.17499999999999999</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="D4">
-        <v>0.20200000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="E4">
-        <v>0.27300000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="F4">
-        <v>0.28899999999999998</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="G4">
-        <v>0.33700000000000002</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="H4">
-        <v>0.35199999999999998</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="I4">
         <v>0.41</v>
       </c>
       <c r="J4">
-        <v>0.41099999999999998</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="D5">
-        <v>6.0000000000000001E-3</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="E5">
-        <v>1.0999999999999999E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="F5">
-        <v>1.4999999999999999E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>3.5999999999999997E-2</v>
+        <v>0.105</v>
       </c>
       <c r="H5">
-        <v>4.4999999999999998E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="I5">
-        <v>3.7999999999999999E-2</v>
+        <v>0.106</v>
       </c>
       <c r="J5">
-        <v>5.3999999999999999E-2</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.216</v>
       </c>
       <c r="C6">
-        <v>0.42399999999999999</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="D6">
-        <v>0.45500000000000002</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="E6">
-        <v>0.47099999999999997</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="F6">
-        <v>0.51100000000000001</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G6">
-        <v>0.58899999999999997</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="H6">
-        <v>0.626</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="I6">
-        <v>0.67300000000000004</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="J6">
-        <v>0.70799999999999996</v>
+        <v>0.69499999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="C7">
-        <v>0.30099999999999999</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="D7">
-        <v>0.38200000000000001</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="E7">
-        <v>0.42699999999999999</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="F7">
-        <v>0.45500000000000002</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="G7">
-        <v>0.53900000000000003</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H7">
         <v>0.58499999999999996</v>
       </c>
       <c r="I7">
-        <v>0.625</v>
+        <v>0.629</v>
       </c>
       <c r="J7">
-        <v>0.66400000000000003</v>
+        <v>0.66800000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="D8">
-        <v>1.2E-2</v>
+        <v>0.151</v>
       </c>
       <c r="E8">
-        <v>0.04</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="F8">
-        <v>5.0999999999999997E-2</v>
+        <v>0.157</v>
       </c>
       <c r="G8">
-        <v>9.2999999999999999E-2</v>
+        <v>0.21</v>
       </c>
       <c r="H8">
-        <v>0.13200000000000001</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="I8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J8">
-        <v>3.7999999999999999E-2</v>
+        <v>0.29699999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="C9">
-        <v>0.40100000000000002</v>
+        <v>0.127</v>
       </c>
       <c r="D9">
-        <v>0.84499999999999997</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E9">
-        <v>0.60599999999999998</v>
+        <v>0.09</v>
       </c>
       <c r="F9">
-        <v>0.17</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G9">
-        <v>0.13100000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H9">
-        <v>0.13800000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="I9">
-        <v>0.13</v>
+        <v>0.114</v>
       </c>
       <c r="J9">
-        <v>0.129</v>
+        <v>0.11899999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p22.xlsx
+++ b/xlsx/Power/p22.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9DD3D8-9670-4A05-92E2-6A8C610F2A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A82D54-1D41-443C-92C3-68B05119787F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3B7641DA-A5C0-4754-89A8-0673DC78D0D2}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{3B7641DA-A5C0-4754-89A8-0673DC78D0D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,106 +398,106 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="B1">
-        <v>0.18099999999999999</v>
+        <v>0.183</v>
       </c>
       <c r="C1">
-        <v>0.26</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="D1">
-        <v>0.34200000000000003</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="E1">
-        <v>0.39600000000000002</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="F1">
-        <v>0.43</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="G1">
-        <v>0.52</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="H1">
         <v>0.53600000000000003</v>
       </c>
       <c r="I1">
-        <v>0.59</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="J1">
-        <v>0.625</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="B2">
-        <v>0.20300000000000001</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="C2">
-        <v>0.29699999999999999</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="D2">
         <v>0.38100000000000001</v>
       </c>
       <c r="E2">
-        <v>0.42599999999999999</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="F2">
-        <v>0.45500000000000002</v>
+        <v>0.45</v>
       </c>
       <c r="G2">
-        <v>0.54400000000000004</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="H2">
-        <v>0.57399999999999995</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="I2">
         <v>0.626</v>
       </c>
       <c r="J2">
-        <v>0.66800000000000004</v>
+        <v>0.67200000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.11600000000000001</v>
+        <v>0.113</v>
       </c>
       <c r="B3">
-        <v>0.14499999999999999</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="C3">
-        <v>0.20499999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="D3">
-        <v>0.25700000000000001</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="E3">
-        <v>0.314</v>
+        <v>0.316</v>
       </c>
       <c r="F3">
-        <v>0.32800000000000001</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="G3">
-        <v>0.39500000000000002</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="H3">
-        <v>0.40899999999999997</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="I3">
-        <v>0.46800000000000003</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="J3">
-        <v>0.48799999999999999</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="B4">
-        <v>0.128</v>
+        <v>0.13</v>
       </c>
       <c r="C4">
         <v>0.17299999999999999</v>
@@ -506,59 +506,59 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="E4">
-        <v>0.27</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="F4">
-        <v>0.28799999999999998</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="G4">
-        <v>0.33800000000000002</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="H4">
-        <v>0.35599999999999998</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="I4">
-        <v>0.41</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="J4">
-        <v>0.41</v>
+        <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>6.0999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>6.9000000000000006E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="C5">
-        <v>7.1999999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>6.8000000000000005E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>9.6000000000000002E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>7.9000000000000001E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="G5">
-        <v>0.105</v>
+        <v>0.01</v>
       </c>
       <c r="H5">
-        <v>9.8000000000000004E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="I5">
-        <v>0.106</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="J5">
-        <v>0.122</v>
+        <v>1.9E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.14199999999999999</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="B6">
         <v>0.216</v>
@@ -567,39 +567,39 @@
         <v>0.32600000000000001</v>
       </c>
       <c r="D6">
-        <v>0.40300000000000002</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="E6">
-        <v>0.44900000000000001</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="F6">
-        <v>0.48799999999999999</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="G6">
-        <v>0.58099999999999996</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="H6">
-        <v>0.61899999999999999</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="I6">
-        <v>0.66600000000000004</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="J6">
-        <v>0.69499999999999995</v>
+        <v>0.69899999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.13800000000000001</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="B7">
         <v>0.21099999999999999</v>
       </c>
       <c r="C7">
-        <v>0.30599999999999999</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="D7">
-        <v>0.38400000000000001</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="E7">
         <v>0.42399999999999999</v>
@@ -608,13 +608,13 @@
         <v>0.45700000000000002</v>
       </c>
       <c r="G7">
-        <v>0.54500000000000004</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="H7">
         <v>0.58499999999999996</v>
       </c>
       <c r="I7">
-        <v>0.629</v>
+        <v>0.628</v>
       </c>
       <c r="J7">
         <v>0.66800000000000004</v>
@@ -634,19 +634,19 @@
         <v>0.151</v>
       </c>
       <c r="E8">
-        <v>0.16600000000000001</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="F8">
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
       <c r="G8">
-        <v>0.21</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="H8">
-        <v>0.23899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="I8">
-        <v>0.28000000000000003</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="J8">
         <v>0.29699999999999999</v>
@@ -657,31 +657,31 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="B9">
-        <v>6.4000000000000001E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="C9">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="D9">
-        <v>9.8000000000000004E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E9">
-        <v>0.09</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="F9">
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G9">
-        <v>0.09</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="H9">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="I9">
-        <v>0.114</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="J9">
-        <v>0.11899999999999999</v>
+        <v>0.121</v>
       </c>
     </row>
   </sheetData>
